--- a/Infosys.xlsx
+++ b/Infosys.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishal\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishal\Documents\INFOSYS-FINANCIAL MODEL &amp; DCF VALUATION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB8BEA5-D0EA-4E01-9E3E-BA66A39BBB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CA816D-353B-43D6-8D19-109B911C0C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASSUMPTIONS" sheetId="20" r:id="rId1"/>
@@ -1813,7 +1813,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2160,23 +2160,20 @@
     <xf numFmtId="9" fontId="35" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="8" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="10" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="14" fillId="8" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="8" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="14" fillId="10" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="14" fillId="8" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="15">
     <cellStyle name="60% - Accent1" xfId="3" builtinId="32"/>
@@ -6284,8 +6281,8 @@
     <col min="7" max="7" width="15.5546875" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" customWidth="1"/>
     <col min="9" max="9" width="12.109375" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="13.109375" customWidth="1"/>
+    <col min="11" max="11" width="13.44140625" customWidth="1"/>
     <col min="16" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6511,23 +6508,23 @@
       </c>
       <c r="G16" s="87">
         <f t="shared" ref="G16:K16" si="4">1/(1+$E$27)^G3</f>
-        <v>0.98247203451551657</v>
+        <v>0.98051549329578314</v>
       </c>
       <c r="H16" s="87">
         <f t="shared" si="4"/>
-        <v>0.94833240715925582</v>
+        <v>0.94267802067680773</v>
       </c>
       <c r="I16" s="87">
         <f t="shared" si="4"/>
-        <v>0.9153790875197324</v>
+        <v>0.9063006721904755</v>
       </c>
       <c r="J16" s="87">
         <f t="shared" si="4"/>
-        <v>0.88357085294433479</v>
+        <v>0.8713271025701721</v>
       </c>
       <c r="K16" s="87">
         <f t="shared" si="4"/>
-        <v>0.85286791321409805</v>
+        <v>0.83770314087747844</v>
       </c>
     </row>
     <row r="18" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6612,9 +6609,9 @@
       <c r="R24" s="80"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="G25" s="183">
+      <c r="G25" s="181">
         <f>E37</f>
-        <v>30260509.58713223</v>
+        <v>5942067.1829307182</v>
       </c>
       <c r="H25" s="11">
         <v>0.01</v>
@@ -6626,7 +6623,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="K25" s="11">
-        <v>4.0300000000000002E-2</v>
+        <v>4.0099999999999997E-2</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.3">
@@ -6640,7 +6637,7 @@
         <v>35236.904047741882</v>
       </c>
       <c r="F26" s="80"/>
-      <c r="G26" s="185">
+      <c r="G26" s="183">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="H26" s="115">
@@ -6650,11 +6647,11 @@
       <c r="I26" s="115">
         <v>-1951519.5422289474</v>
       </c>
-      <c r="J26" s="187">
+      <c r="J26" s="185">
         <v>30249706.652683631</v>
       </c>
-      <c r="K26" s="115">
-        <v>5762879.7165892962</v>
+      <c r="K26" s="184">
+        <v>5986143.0474334862</v>
       </c>
       <c r="M26" s="80"/>
       <c r="N26" s="80"/>
@@ -6671,10 +6668,10 @@
       <c r="D27" s="80"/>
       <c r="E27" s="94">
         <f>WACC!J44</f>
-        <v>3.5999642212509141E-2</v>
+        <v>4.0138278170323248E-2</v>
       </c>
       <c r="F27" s="80"/>
-      <c r="G27" s="185">
+      <c r="G27" s="183">
         <v>0.04</v>
       </c>
       <c r="H27" s="115">
@@ -6687,7 +6684,7 @@
         <v>-7315765.9960549213</v>
       </c>
       <c r="K27" s="115">
-        <v>98522066.098197877</v>
+        <v>295426868.73448205</v>
       </c>
       <c r="M27" s="80"/>
       <c r="N27" s="80"/>
@@ -6707,7 +6704,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="F28" s="80"/>
-      <c r="G28" s="185">
+      <c r="G28" s="183">
         <v>5.7500000000000002E-2</v>
       </c>
       <c r="H28" s="115">
@@ -6716,11 +6713,11 @@
       <c r="I28" s="115">
         <v>-662210.69667593064</v>
       </c>
-      <c r="J28" s="188">
+      <c r="J28" s="185">
         <v>-1200456.495097518</v>
       </c>
       <c r="K28" s="115">
-        <v>-1517637.8191765384</v>
+        <v>-1499392.9617140184</v>
       </c>
       <c r="M28" s="80"/>
       <c r="N28" s="80"/>
@@ -6730,20 +6727,20 @@
       <c r="R28" s="80"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="G29" s="186">
+      <c r="G29" s="183">
         <v>0.06</v>
       </c>
-      <c r="H29" s="184">
+      <c r="H29" s="182">
         <v>-476549.89957148925</v>
       </c>
-      <c r="I29" s="184">
+      <c r="I29" s="182">
         <v>-608489.49477788853</v>
       </c>
-      <c r="J29" s="184">
+      <c r="J29" s="182">
         <v>-1054853.8879318656</v>
       </c>
-      <c r="K29" s="184">
-        <v>-1300002.4952083551</v>
+      <c r="K29" s="182">
+        <v>-1286236.9949543751</v>
       </c>
     </row>
     <row r="30" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6752,12 +6749,12 @@
       </c>
       <c r="C30" s="125"/>
       <c r="D30" s="125"/>
-      <c r="E30" s="182">
+      <c r="E30" s="180">
         <f>E26/(E27-E28)</f>
-        <v>35249515.883583993</v>
+        <v>6857726.0474640979</v>
       </c>
       <c r="F30" s="80"/>
-      <c r="G30" s="185">
+      <c r="G30" s="183">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="H30" s="115">
@@ -6770,7 +6767,7 @@
         <v>-686564.94039521459</v>
       </c>
       <c r="K30" s="115">
-        <v>-795850.63362549199</v>
+        <v>-790061.23286503623</v>
       </c>
       <c r="M30" s="80"/>
       <c r="N30" s="80"/>
@@ -6806,7 +6803,7 @@
       <c r="D36" s="80"/>
       <c r="E36" s="139">
         <f>K16*E30</f>
-        <v>30063181.053439483</v>
+        <v>5744738.6492379708</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
@@ -6817,7 +6814,7 @@
       <c r="D37" s="81"/>
       <c r="E37" s="136">
         <f>SUM(E35:E36)</f>
-        <v>30260509.58713223</v>
+        <v>5942067.1829307182</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
@@ -6850,7 +6847,7 @@
       <c r="D41" s="81"/>
       <c r="E41" s="136">
         <f>E37+E39-E40</f>
-        <v>30277236.58713223</v>
+        <v>5958794.1829307182</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
@@ -6872,7 +6869,7 @@
       <c r="D43" s="80"/>
       <c r="E43" s="139">
         <f>E41/E42</f>
-        <v>74618.980096054787</v>
+        <v>14685.592037206099</v>
       </c>
     </row>
   </sheetData>
@@ -6912,16 +6909,16 @@
       <c r="B1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="180" t="str">
+      <c r="E1" s="186" t="str">
         <f>IF(B2&lt;&gt;B3, "A NEW VERSION OF THE WORKSHEET IS AVAILABLE", "")</f>
         <v/>
       </c>
-      <c r="F1" s="180"/>
-      <c r="G1" s="180"/>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
-      <c r="J1" s="180"/>
-      <c r="K1" s="180"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="186"/>
+      <c r="K1" s="186"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -6930,15 +6927,15 @@
       <c r="B2" s="4">
         <v>2.1</v>
       </c>
-      <c r="E2" s="181" t="s">
+      <c r="E2" s="187" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="181"/>
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
+      <c r="F2" s="187"/>
+      <c r="G2" s="187"/>
+      <c r="H2" s="187"/>
+      <c r="I2" s="187"/>
+      <c r="J2" s="187"/>
+      <c r="K2" s="187"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -14951,6 +14948,38 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{BFA7BF8E-039F-4663-8059-794D1F510143}">
+          <x14:colorSeries theme="1"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="0"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'RATIO ANALYSIS'!D8:L8</xm:f>
+              <xm:sqref>T8</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'RATIO ANALYSIS'!D7:L7</xm:f>
+              <xm:sqref>T7</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'RATIO ANALYSIS'!D6:L6</xm:f>
+              <xm:sqref>T6</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'RATIO ANALYSIS'!D5:L5</xm:f>
+              <xm:sqref>T5</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'RATIO ANALYSIS'!D4:L4</xm:f>
+              <xm:sqref>T4</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{3F98AE7C-6A89-49FA-8C30-2B25DE14DF3A}">
           <x14:colorSeries theme="1"/>
           <x14:colorNegative rgb="FFD00000"/>
@@ -15111,38 +15140,6 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{BFA7BF8E-039F-4663-8059-794D1F510143}">
-          <x14:colorSeries theme="1"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="0"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'RATIO ANALYSIS'!D8:L8</xm:f>
-              <xm:sqref>T8</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'RATIO ANALYSIS'!D7:L7</xm:f>
-              <xm:sqref>T7</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'RATIO ANALYSIS'!D6:L6</xm:f>
-              <xm:sqref>T6</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'RATIO ANALYSIS'!D5:L5</xm:f>
-              <xm:sqref>T5</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'RATIO ANALYSIS'!D4:L4</xm:f>
-              <xm:sqref>T4</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
       </x14:sparklineGroups>
     </ext>
   </extLst>
@@ -21270,8 +21267,8 @@
       <c r="C23" s="80"/>
       <c r="D23" s="80"/>
       <c r="E23" s="92">
-        <f>'Profit &amp; Loss'!K16/WACC!D11</f>
-        <v>4.5335658238884045E-2</v>
+        <f>7.42%</f>
+        <v>7.4200000000000002E-2</v>
       </c>
       <c r="F23" s="80"/>
       <c r="G23" s="80" t="s">
@@ -21299,8 +21296,8 @@
       <c r="H24" s="80"/>
       <c r="I24" s="80"/>
       <c r="J24" s="108">
-        <f>J23-5.73%</f>
-        <v>1.0200000000000001E-2</v>
+        <f>15%-J23</f>
+        <v>8.249999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="16.2" x14ac:dyDescent="0.3">
@@ -21311,7 +21308,7 @@
       <c r="D25" s="100"/>
       <c r="E25" s="103">
         <f>E23*(1-E24)</f>
-        <v>3.3095030514385351E-2</v>
+        <v>5.4165999999999999E-2</v>
       </c>
       <c r="F25" s="80"/>
       <c r="G25" s="80" t="s">
@@ -21337,7 +21334,7 @@
       <c r="I26" s="100"/>
       <c r="J26" s="111">
         <f>J23+(J24*J25)</f>
-        <v>7.4206821909168261E-2</v>
+        <v>0.12174635367709614</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
@@ -21514,7 +21511,7 @@
       <c r="I38" s="80"/>
       <c r="J38" s="112">
         <f>J26</f>
-        <v>7.4206821909168261E-2</v>
+        <v>0.12174635367709614</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
@@ -21563,7 +21560,7 @@
       <c r="I41" s="80"/>
       <c r="J41" s="94">
         <f>E25</f>
-        <v>3.3095030514385351E-2</v>
+        <v>5.4165999999999999E-2</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.3">
@@ -21595,7 +21592,7 @@
       <c r="I44" s="113"/>
       <c r="J44" s="114">
         <f>SUMPRODUCT(J38:J39,J41:J42)</f>
-        <v>3.5999642212509141E-2</v>
+        <v>4.0138278170323248E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Infosys.xlsx
+++ b/Infosys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishal\Documents\INFOSYS-FINANCIAL MODEL &amp; DCF VALUATION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CA816D-353B-43D6-8D19-109B911C0C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3AACC3-876E-4C06-92FA-1E0E9A490C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1404,6 +1404,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4056,24 +4057,24 @@
       <c r="E43" s="120"/>
       <c r="F43" s="120"/>
       <c r="G43" s="121">
-        <f>'RAW FS'!K49</f>
-        <v>-2161</v>
+        <f>-'RAW FS'!K49</f>
+        <v>2161</v>
       </c>
       <c r="H43" s="121">
-        <f>'RAW FS'!L49</f>
-        <v>-2579</v>
+        <f>-'RAW FS'!L49</f>
+        <v>2579</v>
       </c>
       <c r="I43" s="121">
-        <f>'RAW FS'!M49</f>
-        <v>-2201</v>
+        <f>-'RAW FS'!M49</f>
+        <v>2201</v>
       </c>
       <c r="J43" s="121">
-        <f>'RAW FS'!N49</f>
-        <v>-2237</v>
+        <f>-'RAW FS'!N49</f>
+        <v>2237</v>
       </c>
       <c r="K43" s="121">
-        <f>'RAW FS'!O49</f>
-        <v>-2727</v>
+        <f>-'RAW FS'!O49</f>
+        <v>2727</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
@@ -4086,20 +4087,20 @@
       <c r="F44" s="120"/>
       <c r="G44" s="121"/>
       <c r="H44" s="121">
-        <f>H43-G43</f>
-        <v>-418</v>
+        <f>H18-G18</f>
+        <v>5732</v>
       </c>
       <c r="I44" s="121">
-        <f t="shared" ref="I44:K44" si="7">I43-H43</f>
-        <v>378</v>
+        <f t="shared" ref="I44:K44" si="7">I18-H18</f>
+        <v>6566</v>
       </c>
       <c r="J44" s="121">
         <f t="shared" si="7"/>
-        <v>-36</v>
+        <v>-4837</v>
       </c>
       <c r="K44" s="121">
         <f t="shared" si="7"/>
-        <v>-490</v>
+        <v>-563</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
@@ -4219,19 +4220,19 @@
       <c r="G50" s="121"/>
       <c r="H50" s="121">
         <f>SUM(H43:H44)</f>
-        <v>-2997</v>
+        <v>8311</v>
       </c>
       <c r="I50" s="121">
         <f t="shared" ref="I50:K50" si="10">SUM(I43:I44)</f>
-        <v>-1823</v>
+        <v>8767</v>
       </c>
       <c r="J50" s="121">
         <f t="shared" si="10"/>
-        <v>-2273</v>
+        <v>-2600</v>
       </c>
       <c r="K50" s="121">
         <f t="shared" si="10"/>
-        <v>-3217</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
@@ -4257,19 +4258,19 @@
       <c r="G52" s="125"/>
       <c r="H52" s="127">
         <f>H50/H48</f>
-        <v>-0.11890733797536154</v>
+        <v>0.32974270467575234</v>
       </c>
       <c r="I52" s="127">
         <f t="shared" ref="I52:K52" si="11">I50/I48</f>
-        <v>-6.6670323842960844E-2</v>
+        <v>0.32062464571104649</v>
       </c>
       <c r="J52" s="127">
         <f t="shared" si="11"/>
-        <v>-7.9704046567080439E-2</v>
+        <v>-9.1170488814082337E-2</v>
       </c>
       <c r="K52" s="127">
         <f t="shared" si="11"/>
-        <v>-0.10614271691701105</v>
+        <v>7.1399701401433605E-2</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
@@ -4298,7 +4299,7 @@
       </c>
       <c r="K54" s="114">
         <f>AVERAGE(H52:K52)</f>
-        <v>-9.2856106325603469E-2</v>
+        <v>0.15764914074353753</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.3">
@@ -4315,7 +4316,7 @@
       </c>
       <c r="K55" s="114">
         <f>MEDIAN(H52:K52)</f>
-        <v>-9.2923381742045744E-2</v>
+        <v>0.19601217355624007</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.3">
@@ -4358,19 +4359,19 @@
       <c r="G59" s="120"/>
       <c r="H59" s="132">
         <f>H52</f>
-        <v>-0.11890733797536154</v>
+        <v>0.32974270467575234</v>
       </c>
       <c r="I59" s="132">
         <f t="shared" ref="I59:K59" si="13">I52</f>
-        <v>-6.6670323842960844E-2</v>
+        <v>0.32062464571104649</v>
       </c>
       <c r="J59" s="132">
         <f t="shared" si="13"/>
-        <v>-7.9704046567080439E-2</v>
+        <v>-9.1170488814082337E-2</v>
       </c>
       <c r="K59" s="132">
         <f t="shared" si="13"/>
-        <v>-0.10614271691701105</v>
+        <v>7.1399701401433605E-2</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.3">
@@ -4422,19 +4423,19 @@
       <c r="G62" s="125"/>
       <c r="H62" s="133">
         <f>H59*H60</f>
-        <v>-4.3691708853147312E-2</v>
+        <v>0.12116175918535446</v>
       </c>
       <c r="I62" s="133">
         <f t="shared" ref="I62:K62" si="15">I59*I60</f>
-        <v>-2.4242666028351813E-2</v>
+        <v>0.1165855474879651</v>
       </c>
       <c r="J62" s="133">
         <f t="shared" si="15"/>
-        <v>-2.9401112404604839E-2</v>
+        <v>-3.3630836890441086E-2</v>
       </c>
       <c r="K62" s="133">
         <f t="shared" si="15"/>
-        <v>-3.9047185556061299E-2</v>
+        <v>2.6266120467303901E-2</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.3">
@@ -4443,7 +4444,7 @@
       </c>
       <c r="K64" s="114">
         <f>AVERAGE(H62:K62)</f>
-        <v>-3.4095668210541316E-2</v>
+        <v>5.7595647562545593E-2</v>
       </c>
     </row>
     <row r="65" spans="10:11" x14ac:dyDescent="0.3">
@@ -4452,7 +4453,7 @@
       </c>
       <c r="K65" s="114">
         <f>MEDIAN(H62:K62)</f>
-        <v>-3.4224148980333068E-2</v>
+        <v>7.1425833977634495E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6440,27 +6441,27 @@
       <c r="E12" s="80"/>
       <c r="F12" s="94">
         <f>'INTRINSIC GROWTH'!K55</f>
-        <v>-9.2923381742045744E-2</v>
+        <v>0.19601217355624007</v>
       </c>
       <c r="G12" s="94">
         <f>F12</f>
-        <v>-9.2923381742045744E-2</v>
+        <v>0.19601217355624007</v>
       </c>
       <c r="H12" s="94">
         <f t="shared" ref="H12:K12" si="2">G12</f>
-        <v>-9.2923381742045744E-2</v>
+        <v>0.19601217355624007</v>
       </c>
       <c r="I12" s="94">
         <f t="shared" si="2"/>
-        <v>-9.2923381742045744E-2</v>
+        <v>0.19601217355624007</v>
       </c>
       <c r="J12" s="94">
         <f t="shared" si="2"/>
-        <v>-9.2923381742045744E-2</v>
+        <v>0.19601217355624007</v>
       </c>
       <c r="K12" s="94">
         <f t="shared" si="2"/>
-        <v>-9.2923381742045744E-2</v>
+        <v>0.19601217355624007</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6472,27 +6473,27 @@
       <c r="E14" s="125"/>
       <c r="F14" s="137">
         <f>F10*(1-F12)</f>
-        <v>33124.595084683358</v>
+        <v>24367.464040814084</v>
       </c>
       <c r="G14" s="137">
         <f t="shared" ref="G14:K14" si="3">G10*(1-G12)</f>
-        <v>35260.167372607335</v>
+        <v>25938.456253685203</v>
       </c>
       <c r="H14" s="137">
         <f t="shared" si="3"/>
-        <v>37362.937055578332</v>
+        <v>27485.317868292612</v>
       </c>
       <c r="I14" s="137">
         <f t="shared" si="3"/>
-        <v>39465.706738549357</v>
+        <v>29032.179482900036</v>
       </c>
       <c r="J14" s="137">
         <f t="shared" si="3"/>
-        <v>41568.476421520434</v>
+        <v>30579.041097507499</v>
       </c>
       <c r="K14" s="137">
         <f t="shared" si="3"/>
-        <v>43671.246104491453</v>
+        <v>32125.902712114916</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
@@ -6611,7 +6612,7 @@
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="G25" s="181">
         <f>E37</f>
-        <v>5942067.1829307182</v>
+        <v>4371166.1391784772</v>
       </c>
       <c r="H25" s="11">
         <v>0.01</v>
@@ -6634,7 +6635,7 @@
       <c r="D26" s="80"/>
       <c r="E26" s="135">
         <f>F14*(1+E20)</f>
-        <v>35236.904047741882</v>
+        <v>25921.343041261644</v>
       </c>
       <c r="F26" s="80"/>
       <c r="G26" s="183">
@@ -6642,16 +6643,16 @@
       </c>
       <c r="H26" s="115">
         <f t="dataTable" ref="H26:K30" dt2D="1" dtr="1" r1="E27" r2="E28"/>
-        <v>-1150428.3328357253</v>
+        <v>-846290.22514061036</v>
       </c>
       <c r="I26" s="115">
-        <v>-1951519.5422289474</v>
+        <v>-1435597.3906590743</v>
       </c>
       <c r="J26" s="185">
-        <v>30249706.652683631</v>
+        <v>22252608.287588645</v>
       </c>
       <c r="K26" s="184">
-        <v>5986143.0474334862</v>
+        <v>4403589.6915447246</v>
       </c>
       <c r="M26" s="80"/>
       <c r="N26" s="80"/>
@@ -6675,16 +6676,16 @@
         <v>0.04</v>
       </c>
       <c r="H27" s="115">
-        <v>-925802.18841431336</v>
+        <v>-681048.3713814253</v>
       </c>
       <c r="I27" s="115">
-        <v>-1414307.5232485237</v>
+        <v>-1040407.8186406811</v>
       </c>
       <c r="J27" s="115">
-        <v>-7315765.9960549213</v>
+        <v>-5381700.9501289977</v>
       </c>
       <c r="K27" s="115">
-        <v>295426868.73448205</v>
+        <v>217325029.39806452</v>
       </c>
       <c r="M27" s="80"/>
       <c r="N27" s="80"/>
@@ -6708,16 +6709,16 @@
         <v>5.7500000000000002E-2</v>
       </c>
       <c r="H28" s="115">
-        <v>-512017.18553276471</v>
+        <v>-376655.48287766316</v>
       </c>
       <c r="I28" s="115">
-        <v>-662210.69667593064</v>
+        <v>-487142.41781492962</v>
       </c>
       <c r="J28" s="185">
-        <v>-1200456.495097518</v>
+        <v>-883092.46957033721</v>
       </c>
       <c r="K28" s="115">
-        <v>-1499392.9617140184</v>
+        <v>-1102999.2663822877</v>
       </c>
       <c r="M28" s="80"/>
       <c r="N28" s="80"/>
@@ -6731,16 +6732,16 @@
         <v>0.06</v>
       </c>
       <c r="H29" s="182">
-        <v>-476549.89957148925</v>
+        <v>-350564.66386305512</v>
       </c>
       <c r="I29" s="182">
-        <v>-608489.49477788853</v>
+        <v>-447623.46061309054</v>
       </c>
       <c r="J29" s="182">
-        <v>-1054853.8879318656</v>
+        <v>-775982.74384275009</v>
       </c>
       <c r="K29" s="182">
-        <v>-1286236.9949543751</v>
+        <v>-946195.2257042994</v>
       </c>
     </row>
     <row r="30" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6751,23 +6752,23 @@
       <c r="D30" s="125"/>
       <c r="E30" s="180">
         <f>E26/(E27-E28)</f>
-        <v>6857726.0474640979</v>
+        <v>5044752.7716528736</v>
       </c>
       <c r="F30" s="80"/>
       <c r="G30" s="183">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="H30" s="115">
-        <v>-364236.82736078306</v>
+        <v>-267943.73698346247</v>
       </c>
       <c r="I30" s="115">
-        <v>-447325.88908376131</v>
+        <v>-329066.58900757227</v>
       </c>
       <c r="J30" s="115">
-        <v>-686564.94039521459</v>
+        <v>-505058.14347297046</v>
       </c>
       <c r="K30" s="115">
-        <v>-790061.23286503623</v>
+        <v>-581193.17783847998</v>
       </c>
       <c r="M30" s="80"/>
       <c r="N30" s="80"/>
@@ -6792,7 +6793,7 @@
       <c r="D35" s="80"/>
       <c r="E35" s="135">
         <f>SUM(G14:K14)</f>
-        <v>197328.53369274695</v>
+        <v>145160.89741450024</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
@@ -6803,7 +6804,7 @@
       <c r="D36" s="80"/>
       <c r="E36" s="139">
         <f>K16*E30</f>
-        <v>5744738.6492379708</v>
+        <v>4226005.2417639773</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
@@ -6814,7 +6815,7 @@
       <c r="D37" s="81"/>
       <c r="E37" s="136">
         <f>SUM(E35:E36)</f>
-        <v>5942067.1829307182</v>
+        <v>4371166.1391784772</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
@@ -6847,7 +6848,7 @@
       <c r="D41" s="81"/>
       <c r="E41" s="136">
         <f>E37+E39-E40</f>
-        <v>5958794.1829307182</v>
+        <v>4387893.1391784772</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
@@ -6869,7 +6870,7 @@
       <c r="D43" s="80"/>
       <c r="E43" s="139">
         <f>E41/E42</f>
-        <v>14685.592037206099</v>
+        <v>10814.068512287118</v>
       </c>
     </row>
   </sheetData>
@@ -14948,38 +14949,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{BFA7BF8E-039F-4663-8059-794D1F510143}">
-          <x14:colorSeries theme="1"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="0"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'RATIO ANALYSIS'!D8:L8</xm:f>
-              <xm:sqref>T8</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'RATIO ANALYSIS'!D7:L7</xm:f>
-              <xm:sqref>T7</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'RATIO ANALYSIS'!D6:L6</xm:f>
-              <xm:sqref>T6</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'RATIO ANALYSIS'!D5:L5</xm:f>
-              <xm:sqref>T5</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'RATIO ANALYSIS'!D4:L4</xm:f>
-              <xm:sqref>T4</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{3F98AE7C-6A89-49FA-8C30-2B25DE14DF3A}">
           <x14:colorSeries theme="1"/>
           <x14:colorNegative rgb="FFD00000"/>
@@ -15140,6 +15109,38 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{BFA7BF8E-039F-4663-8059-794D1F510143}">
+          <x14:colorSeries theme="1"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="0"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'RATIO ANALYSIS'!D8:L8</xm:f>
+              <xm:sqref>T8</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'RATIO ANALYSIS'!D7:L7</xm:f>
+              <xm:sqref>T7</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'RATIO ANALYSIS'!D6:L6</xm:f>
+              <xm:sqref>T6</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'RATIO ANALYSIS'!D5:L5</xm:f>
+              <xm:sqref>T5</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'RATIO ANALYSIS'!D4:L4</xm:f>
+              <xm:sqref>T4</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
       </x14:sparklineGroups>
     </ext>
   </extLst>
